--- a/Deliverables/BOM/LCSC_BOM-v2.1.xlsx
+++ b/Deliverables/BOM/LCSC_BOM-v2.1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6BCC9D-0013-41D2-A7E2-1D5CD753EE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D07073-DDE2-4B3C-ACF1-C1386628C86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20 Boards" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>MOQ (5K Boards)</t>
+  </si>
+  <si>
+    <t>C318893</t>
+  </si>
+  <si>
+    <t>C123008</t>
   </si>
 </sst>
 </file>
@@ -205,7 +211,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -271,11 +277,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -302,6 +319,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -590,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C0EAC8-2749-4D8B-AD6B-98E76B44D0B5}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -824,87 +844,87 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4">
-        <v>180</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="5">
-        <v>90</v>
+      <c r="B23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="4">
-        <v>40</v>
+      <c r="B24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="5">
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>1</v>
+      <c r="B25" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="7">
-        <v>100</v>
+      <c r="B26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="5">
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>200</v>
+      <c r="B27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="4">
-        <v>100</v>
+      <c r="B28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="5">
+        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="5">
-        <v>300</v>
+      <c r="B29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -912,10 +932,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C30" s="4">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -923,10 +943,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C31" s="5">
-        <v>400</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -934,139 +954,64 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C32" s="4">
-        <v>100</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>1</v>
+      <c r="B33" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="5">
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>32</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4">
-        <v>22</v>
+      <c r="B34" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="5">
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="5">
-        <v>22</v>
+      <c r="B35" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="4">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="4">
-        <v>165</v>
+      <c r="B36" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="5">
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>35</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+      <c r="B37" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>38</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>40</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="4">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>42</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="8">
+      <c r="C37" s="4">
         <v>45</v>
       </c>
     </row>
@@ -1089,7 +1034,7 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1144,7 +1089,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="9">
@@ -1177,7 +1122,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="7">
@@ -1199,7 +1144,7 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="7">
@@ -1221,7 +1166,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="7">
@@ -1243,7 +1188,7 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="7">
@@ -1364,7 +1309,7 @@
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="9">
@@ -1453,7 +1398,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C34" s="5">
         <v>1020</v>
@@ -1464,7 +1409,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C35" s="4">
         <v>8020</v>
@@ -1485,7 +1430,9 @@
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
+      <c r="B37" s="4" t="s">
+        <v>1</v>
+      </c>
       <c r="C37" s="4">
         <v>1020</v>
       </c>
@@ -1506,7 +1453,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C39" s="4">
         <v>1020</v>
@@ -1549,7 +1496,7 @@
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C43" s="8">

--- a/Deliverables/BOM/LCSC_BOM-v2.1.xlsx
+++ b/Deliverables/BOM/LCSC_BOM-v2.1.xlsx
@@ -8,21 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D07073-DDE2-4B3C-ACF1-C1386628C86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C954E06A-EBF0-4AF8-BCFF-0C5EED4B67D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20 Boards" sheetId="2" r:id="rId1"/>
-    <sheet name="1K Boards" sheetId="3" r:id="rId2"/>
-    <sheet name="5K Boards" sheetId="4" r:id="rId3"/>
+    <sheet name="5 Boards" sheetId="5" r:id="rId1"/>
+    <sheet name="20 Boards" sheetId="2" r:id="rId2"/>
+    <sheet name="1K Boards" sheetId="3" r:id="rId3"/>
+    <sheet name="5K Boards" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="43">
   <si>
     <t>#</t>
   </si>
@@ -147,14 +161,17 @@
     <t>C318893</t>
   </si>
   <si>
-    <t>C123008</t>
+    <t>C492405</t>
+  </si>
+  <si>
+    <t>MOQ (5 Boards)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +197,14 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -323,6 +348,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,8 +637,397 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94F98A7-C992-4BA5-BE2B-007CDD4D1867}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="8">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C0EAC8-2749-4D8B-AD6B-98E76B44D0B5}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -623,10 +1040,10 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="10" t="s">
         <v>37</v>
       </c>
     </row>
@@ -726,7 +1143,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="5">
-        <v>160</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -788,21 +1205,21 @@
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="5">
-        <v>100</v>
+      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="4">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="B18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5">
         <v>30</v>
       </c>
     </row>
@@ -810,33 +1227,33 @@
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="5">
-        <v>30</v>
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4">
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="4">
-        <v>40</v>
+      <c r="B20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="5">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="5">
-        <v>30</v>
+      <c r="B21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="4">
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -844,76 +1261,76 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="4">
-        <v>40</v>
+        <v>23</v>
+      </c>
+      <c r="C22" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="7">
-        <v>100</v>
+      <c r="B23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="5">
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="5">
-        <v>200</v>
+      <c r="B24" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="4">
-        <v>100</v>
+      <c r="B25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="5">
+        <v>300</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="5">
-        <v>300</v>
+      <c r="B26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="4">
-        <v>100</v>
+      <c r="B27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="5">
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="5">
-        <v>400</v>
+      <c r="B28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -921,43 +1338,43 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C29" s="4">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>28</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="4">
+      <c r="B30" s="5" t="s">
         <v>30</v>
+      </c>
+      <c r="C30" s="5">
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="5">
-        <v>22</v>
+      <c r="B31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="4">
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="4">
-        <v>165</v>
+      <c r="B32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="5">
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -965,10 +1382,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C33" s="5">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -976,10 +1393,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C34" s="5">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -987,31 +1404,9 @@
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C35" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>34</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>35</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="4">
         <v>45</v>
       </c>
     </row>
@@ -1020,7 +1415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BFFE53-9D27-42F3-92BE-BCB6B78E7DFA}">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1508,7 +1903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97F5C245-404B-4B74-AFB5-D72945D249AF}">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Deliverables/BOM/LCSC_BOM-v2.1.xlsx
+++ b/Deliverables/BOM/LCSC_BOM-v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C954E06A-EBF0-4AF8-BCFF-0C5EED4B67D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB49EF9-8F49-489D-B786-668F370BA2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="44">
   <si>
     <t>#</t>
   </si>
@@ -149,9 +149,6 @@
     <t>C390772</t>
   </si>
   <si>
-    <t>MOQ (20 Boards)</t>
-  </si>
-  <si>
     <t>MOQ (1K Boards)</t>
   </si>
   <si>
@@ -165,6 +162,12 @@
   </si>
   <si>
     <t>MOQ (5 Boards)</t>
+  </si>
+  <si>
+    <t>C2168289</t>
+  </si>
+  <si>
+    <t>C113030</t>
   </si>
 </sst>
 </file>
@@ -236,7 +239,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -313,11 +316,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -350,6 +366,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -654,121 +676,121 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="5">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="C3" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="C4" s="5">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="C5" s="4">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="C7" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
-        <v>9</v>
-      </c>
       <c r="B10" s="5" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C10" s="5">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -779,244 +801,244 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="C14" s="5">
+      <c r="B16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="4">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="C18" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
+      <c r="B21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="C19" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11">
-        <v>21</v>
-      </c>
       <c r="B22" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="4">
+      <c r="B23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="4">
+      <c r="B25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="C27" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="11">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="C29" s="5">
+      <c r="B31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="4">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="s">
+    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="C31" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="11">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="11">
-        <v>32</v>
-      </c>
       <c r="B33" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="5">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="13">
         <v>15</v>
       </c>
     </row>
@@ -1027,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C0EAC8-2749-4D8B-AD6B-98E76B44D0B5}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -1037,378 +1059,169 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>37</v>
-      </c>
+      <c r="A2" s="3"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5">
-        <v>450</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4">
-        <v>40</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5">
-        <v>900</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4">
-        <v>300</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="5">
-        <v>45</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4">
-        <v>400</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>30</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4">
-        <v>200</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="5">
-        <v>230</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="4">
-        <v>100</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="5">
-        <v>100</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="4">
-        <v>200</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="5">
-        <v>200</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="4">
-        <v>170</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="4">
-        <v>30</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="5">
-        <v>30</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="4">
-        <v>40</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>18</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="5">
-        <v>30</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="4">
-        <v>40</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="7">
-        <v>100</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="5">
-        <v>200</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>22</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="4">
-        <v>100</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="5">
-        <v>300</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>24</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="4">
-        <v>100</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>25</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="5">
-        <v>400</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>26</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="4">
-        <v>100</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="4">
-        <v>30</v>
-      </c>
+      <c r="A29" s="2"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>28</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="5">
-        <v>22</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="4">
-        <v>165</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>30</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="5">
-        <v>22</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>31</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="5">
-        <v>42</v>
-      </c>
+      <c r="A33" s="2"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>32</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="4">
-        <v>45</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1433,7 +1246,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1921,7 +1734,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/Deliverables/BOM/LCSC_BOM-v2.1.xlsx
+++ b/Deliverables/BOM/LCSC_BOM-v2.1.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB49EF9-8F49-489D-B786-668F370BA2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="5" r:id="rId1"/>
-    <sheet name="20 Boards" sheetId="2" r:id="rId2"/>
-    <sheet name="1K Boards" sheetId="3" r:id="rId3"/>
-    <sheet name="5K Boards" sheetId="4" r:id="rId4"/>
+    <sheet name="10 Boards" sheetId="6" r:id="rId2"/>
+    <sheet name="20 Boards" sheetId="2" r:id="rId3"/>
+    <sheet name="1K Boards" sheetId="3" r:id="rId4"/>
+    <sheet name="5K Boards" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="44">
   <si>
     <t>#</t>
   </si>
@@ -164,16 +164,16 @@
     <t>MOQ (5 Boards)</t>
   </si>
   <si>
-    <t>C2168289</t>
-  </si>
-  <si>
     <t>C113030</t>
+  </si>
+  <si>
+    <t>MOQ (10 Boards)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -333,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -369,9 +369,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -659,17 +656,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94F98A7-C992-4BA5-BE2B-007CDD4D1867}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -772,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5">
         <v>60</v>
@@ -838,7 +836,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="5">
         <v>20</v>
@@ -1014,10 +1012,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1025,20 +1023,20 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="5">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>33</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="5">
         <v>15</v>
       </c>
     </row>
@@ -1048,8 +1046,397 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C0EAC8-2749-4D8B-AD6B-98E76B44D0B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="5">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -1059,177 +1446,318 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" s="5"/>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="C8" s="5"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="5"/>
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="5"/>
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="5"/>
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="5"/>
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="C24" s="5"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="5"/>
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="5"/>
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C28" s="5"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="5"/>
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="C29" s="5"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="5"/>
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="C30" s="5"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="5"/>
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="5"/>
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="C32" s="5"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="5"/>
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="C33" s="5"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="5"/>
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BFFE53-9D27-42F3-92BE-BCB6B78E7DFA}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1716,8 +2244,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97F5C245-404B-4B74-AFB5-D72945D249AF}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
